--- a/courier.xlsx
+++ b/courier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EBB85E-3EF7-4DD2-91BF-2483610E4611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F775314A-C64E-4434-AEC0-D9FF4E3B97B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>company</t>
   </si>
@@ -49,6 +49,45 @@
   </si>
   <si>
     <t>096-694-6499</t>
+  </si>
+  <si>
+    <t>Aramex</t>
+  </si>
+  <si>
+    <t>Call Center</t>
+  </si>
+  <si>
+    <t>02-022-7070</t>
+  </si>
+  <si>
+    <t>Charinda (Nan)(Sales)</t>
+  </si>
+  <si>
+    <t>charinda@aramex.com</t>
+  </si>
+  <si>
+    <t>061-326-9162</t>
+  </si>
+  <si>
+    <t>K. โอ(Operation)</t>
+  </si>
+  <si>
+    <t>Pimphisa@aramex.com</t>
+  </si>
+  <si>
+    <t>066-110-4321</t>
+  </si>
+  <si>
+    <t>Fedex</t>
+  </si>
+  <si>
+    <t>K. Jichada(Sales)</t>
+  </si>
+  <si>
+    <t>jichada.pongsuradate@fedex.com</t>
+  </si>
+  <si>
+    <t>089-697-0223</t>
   </si>
 </sst>
 </file>
@@ -387,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -424,9 +463,65 @@
         <v>7</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{E5BF9FF3-0BC3-4B11-ACE6-11B5FC3EE0FF}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{7526ED5F-D42D-44A7-909D-36570098FC7B}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{887A14BF-3AAD-41B4-B95C-69EABFF132D4}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{7B6204BD-97BE-4CCC-9F6D-A9AC1D1A8C6F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/courier.xlsx
+++ b/courier.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/courier.xlsx
+++ b/courier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F775314A-C64E-4434-AEC0-D9FF4E3B97B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D117A8A8-5EE2-45C2-ABD3-E5A49543600F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>company</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>089-697-0223</t>
+  </si>
+  <si>
+    <t>tle</t>
   </si>
 </sst>
 </file>
@@ -426,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -516,6 +519,20 @@
         <v>20</v>
       </c>
     </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{E5BF9FF3-0BC3-4B11-ACE6-11B5FC3EE0FF}"/>

--- a/courier.xlsx
+++ b/courier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D117A8A8-5EE2-45C2-ABD3-E5A49543600F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA51254-225B-40CE-88FF-7242F15F436B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8505" yWindow="240" windowWidth="8985" windowHeight="10680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>company</t>
   </si>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t>089-697-0223</t>
-  </si>
-  <si>
-    <t>tle</t>
   </si>
 </sst>
 </file>
@@ -429,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -519,20 +516,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{E5BF9FF3-0BC3-4B11-ACE6-11B5FC3EE0FF}"/>
